--- a/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>18.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>18.2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>18.5</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>18.9</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>18.7</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -750,7 +750,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>18.2</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29">
-        <v>18.5</v>
+      <c r="D29" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
-        <v>4</v>
+      <c r="D36">
+        <v>18.7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -917,8 +917,8 @@
       <c r="C38">
         <v>8</v>
       </c>
-      <c r="D38" t="s">
-        <v>4</v>
+      <c r="D38">
+        <v>18.1</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -973,8 +973,8 @@
       <c r="C42">
         <v>12</v>
       </c>
-      <c r="D42" t="s">
-        <v>4</v>
+      <c r="D42">
+        <v>19.4</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -987,8 +987,8 @@
       <c r="C43">
         <v>13</v>
       </c>
-      <c r="D43" t="s">
-        <v>4</v>
+      <c r="D43">
+        <v>19.8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1015,8 +1015,8 @@
       <c r="C45">
         <v>15</v>
       </c>
-      <c r="D45" t="s">
-        <v>4</v>
+      <c r="D45">
+        <v>19.5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1029,8 +1029,8 @@
       <c r="C46">
         <v>16</v>
       </c>
-      <c r="D46" t="s">
-        <v>4</v>
+      <c r="D46">
+        <v>19.3</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1072,7 +1072,7 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1085,8 +1085,8 @@
       <c r="C50">
         <v>20</v>
       </c>
-      <c r="D50" t="s">
-        <v>4</v>
+      <c r="D50">
+        <v>18.5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>26</v>
       </c>
       <c r="D56">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1197,8 +1197,8 @@
       <c r="C58">
         <v>28</v>
       </c>
-      <c r="D58" t="s">
-        <v>4</v>
+      <c r="D58">
+        <v>18.1</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1211,8 +1211,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59">
-        <v>18.6</v>
+      <c r="D59" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>16.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>18.15</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -554,7 +554,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>18.7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>18.7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -694,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -750,7 +750,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>18.5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36">
-        <v>18.7</v>
+      <c r="D36" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -946,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="D42">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1099,8 +1099,8 @@
       <c r="C51">
         <v>21</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>18.5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1127,8 +1127,8 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="D53" t="s">
-        <v>4</v>
+      <c r="D53">
+        <v>17.4</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>26</v>
       </c>
       <c r="D56">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1211,8 +1211,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59" t="s">
-        <v>4</v>
+      <c r="D59">
+        <v>18.7</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1226,7 +1226,7 @@
         <v>30</v>
       </c>
       <c r="D60">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Avg_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -889,8 +886,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
-        <v>4</v>
+      <c r="D36">
+        <v>18.4</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1100,7 +1097,7 @@
         <v>21</v>
       </c>
       <c r="D51">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="52" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Avg_Temperature_timeseries.xlsx
@@ -1097,7 +1097,7 @@
         <v>21</v>
       </c>
       <c r="D51">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
